--- a/docs/management/Technical_Bill_of_Materials.xlsx
+++ b/docs/management/Technical_Bill_of_Materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UOW\CSIT214 IT Project Management\FlyDreamAir\docs\management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92AE126-C73F-4037-A65C-0EFF0D8140ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1687E9-C868-4FB3-A3CE-92C4BD25ACB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D00B59A3-D2CE-4B40-9E72-2D366F0F726D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D00B59A3-D2CE-4B40-9E72-2D366F0F726D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Item</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>$100 / month</t>
+  </si>
+  <si>
+    <t>1200/year</t>
   </si>
 </sst>
 </file>
@@ -574,12 +577,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8927181-3F83-4B9F-8A5E-EEACD5CFA8CF}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="100.42578125" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
     <col min="4" max="4" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -695,6 +698,11 @@
         <v>28</v>
       </c>
     </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
